--- a/Horario/Horario 2026.xlsx
+++ b/Horario/Horario 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maria Alejandra\Downloads\Pagina Web de Riesgo VS\Horario\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F415E32A-6A93-47AC-A4D2-8B6788D6AAE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{155C489B-A603-49D9-81E7-222D9BA7A249}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9AAEFA76-0198-46F6-BBF5-EADAB38A6758}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9AAEFA76-0198-46F6-BBF5-EADAB38A6758}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="26">
   <si>
     <t>GESTOR</t>
   </si>
@@ -115,12 +115,15 @@
   <si>
     <t xml:space="preserve">Juan Jose </t>
   </si>
+  <si>
+    <t>Dia de la Familia</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -170,6 +173,14 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -279,7 +290,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -302,6 +313,7 @@
     <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -646,17 +658,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B1D5CB7-A214-4F9F-A075-10C6E5CC7E55}">
-  <dimension ref="A1:O51"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:O64"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.5546875" bestFit="1" customWidth="1"/>
     <col min="2" max="6" width="12" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17" bestFit="1" customWidth="1"/>
     <col min="8" max="15" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
@@ -702,8 +714,8 @@
         <v>46138</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="11"/>
+    <row r="2" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="12"/>
       <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
@@ -747,7 +759,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
@@ -794,7 +806,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>12</v>
       </c>
@@ -841,7 +853,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>14</v>
       </c>
@@ -888,7 +900,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>15</v>
       </c>
@@ -935,7 +947,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>17</v>
       </c>
@@ -982,7 +994,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>18</v>
       </c>
@@ -1029,7 +1041,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>20</v>
       </c>
@@ -1076,7 +1088,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>21</v>
       </c>
@@ -1123,7 +1135,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>22</v>
       </c>
@@ -1170,7 +1182,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>23</v>
       </c>
@@ -1217,8 +1229,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="10" t="s">
+    <row r="14" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="11" t="s">
         <v>0</v>
       </c>
       <c r="B14" s="1">
@@ -1243,8 +1255,8 @@
         <v>46145</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="11"/>
+    <row r="15" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="12"/>
       <c r="B15" s="2" t="s">
         <v>1</v>
       </c>
@@ -1267,7 +1279,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>17</v>
       </c>
@@ -1293,7 +1305,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>8</v>
       </c>
@@ -1319,7 +1331,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>12</v>
       </c>
@@ -1345,7 +1357,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>15</v>
       </c>
@@ -1371,7 +1383,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>18</v>
       </c>
@@ -1397,7 +1409,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>23</v>
       </c>
@@ -1423,7 +1435,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>21</v>
       </c>
@@ -1449,7 +1461,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>22</v>
       </c>
@@ -1475,7 +1487,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>14</v>
       </c>
@@ -1501,7 +1513,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>20</v>
       </c>
@@ -1527,8 +1539,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="10" t="s">
+    <row r="27" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A27" s="11" t="s">
         <v>0</v>
       </c>
       <c r="B27" s="1">
@@ -1553,8 +1565,8 @@
         <v>46152</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A28" s="11"/>
+    <row r="28" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A28" s="12"/>
       <c r="B28" s="2" t="s">
         <v>1</v>
       </c>
@@ -1577,7 +1589,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>22</v>
       </c>
@@ -1603,7 +1615,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>14</v>
       </c>
@@ -1629,7 +1641,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
         <v>20</v>
       </c>
@@ -1655,7 +1667,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>15</v>
       </c>
@@ -1681,7 +1693,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
         <v>18</v>
       </c>
@@ -1707,7 +1719,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>21</v>
       </c>
@@ -1733,7 +1745,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
         <v>8</v>
       </c>
@@ -1759,7 +1771,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>12</v>
       </c>
@@ -1785,7 +1797,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
         <v>23</v>
       </c>
@@ -1811,7 +1823,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>17</v>
       </c>
@@ -1837,8 +1849,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="12" t="s">
+    <row r="40" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A40" s="13" t="s">
         <v>0</v>
       </c>
       <c r="B40" s="1">
@@ -1863,8 +1875,8 @@
         <v>46159</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A41" s="12"/>
+    <row r="41" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A41" s="13"/>
       <c r="B41" s="2" t="s">
         <v>1</v>
       </c>
@@ -1887,7 +1899,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
         <v>22</v>
       </c>
@@ -1913,7 +1925,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
         <v>12</v>
       </c>
@@ -1939,7 +1951,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>18</v>
       </c>
@@ -1965,7 +1977,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
         <v>23</v>
       </c>
@@ -1973,7 +1985,7 @@
         <v>9</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D45" s="4" t="s">
         <v>9</v>
@@ -1984,14 +1996,14 @@
       <c r="F45" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G45" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="H45" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="G45" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H45" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>15</v>
       </c>
@@ -2017,7 +2029,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
         <v>24</v>
       </c>
@@ -2043,7 +2055,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>14</v>
       </c>
@@ -2069,7 +2081,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
         <v>21</v>
       </c>
@@ -2095,7 +2107,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>20</v>
       </c>
@@ -2103,7 +2115,7 @@
         <v>11</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D50" s="4" t="s">
         <v>11</v>
@@ -2114,14 +2126,14 @@
       <c r="F50" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G50" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="H50" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="G50" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H50" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
         <v>8</v>
       </c>
@@ -2147,12 +2159,323 @@
         <v>9</v>
       </c>
     </row>
+    <row r="53" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A53" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B53" s="1">
+        <v>46160</v>
+      </c>
+      <c r="C53" s="1">
+        <v>46161</v>
+      </c>
+      <c r="D53" s="1">
+        <v>46162</v>
+      </c>
+      <c r="E53" s="1">
+        <v>46163</v>
+      </c>
+      <c r="F53" s="1">
+        <v>46164</v>
+      </c>
+      <c r="G53" s="1">
+        <v>46165</v>
+      </c>
+      <c r="H53" s="1">
+        <v>46166</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A54" s="13"/>
+      <c r="B54" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A55" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E55" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F55" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G55" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H55" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A56" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E56" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F56" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G56" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H56" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A57" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E57" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G57" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H57" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A58" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E58" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F58" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G58" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H58" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A59" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E59" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F59" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G59" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H59" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A60" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E60" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F60" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G60" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H60" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A61" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E61" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F61" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G61" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H61" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A62" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E62" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F62" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G62" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H62" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A63" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E63" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F63" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G63" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H63" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A64" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B64" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C64" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D64" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E64" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F64" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G64" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="H64" s="7" t="s">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="A14:A15"/>
     <mergeCell ref="A27:A28"/>
     <mergeCell ref="A40:A41"/>
+    <mergeCell ref="A53:A54"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2160,6 +2483,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9d4e7416-6feb-444a-9f0d-6e119e2a4ded">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="ab20b492-db1c-4b70-84db-283da62d5dcb" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A49D20B196870C459C080BD3A88F41F5" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c891d3af3c5d8789d4a1386f5525110a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9d4e7416-6feb-444a-9f0d-6e119e2a4ded" xmlns:ns3="ab20b492-db1c-4b70-84db-283da62d5dcb" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a2d778173b158e0f4887e6c1a7be78b9" ns2:_="" ns3:_="">
     <xsd:import namespace="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
@@ -2360,7 +2694,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -2369,18 +2703,18 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9d4e7416-6feb-444a-9f0d-6e119e2a4ded">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="ab20b492-db1c-4b70-84db-283da62d5dcb" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E7BE3CC-8834-4B2B-B0A5-EDC239DF005F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
+    <ds:schemaRef ds:uri="ab20b492-db1c-4b70-84db-283da62d5dcb"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D90F563-717D-4F15-9FD2-892B1218D415}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2399,21 +2733,10 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E90FB8C-E259-434B-8A97-2530AD5FA4BD}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E7BE3CC-8834-4B2B-B0A5-EDC239DF005F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="9d4e7416-6feb-444a-9f0d-6e119e2a4ded"/>
-    <ds:schemaRef ds:uri="ab20b492-db1c-4b70-84db-283da62d5dcb"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>